--- a/server/excel/release/wish-gift.xlsx
+++ b/server/excel/release/wish-gift.xlsx
@@ -1,82 +1,81 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12540"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="心愿之礼每日礼包" sheetId="1" r:id="rId1"/>
+    <sheet name="心愿之礼每日礼包" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>奖励配置</t>
-  </si>
-  <si>
-    <t>发放天数</t>
-  </si>
-  <si>
-    <t>邮件ID</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>3:590008:1#6:30002:1#3:100025:1</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3:590008:1#3:400036:10#3:20001:1</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0:1:100#3:100022:2#0:0:1000000</t>
-  </si>
-  <si>
-    <t>Tâm nguyện gói quà</t>
-  </si>
-  <si>
-    <t>Cầu nguyện gói quà</t>
-  </si>
-  <si>
-    <t>Cầu nguyện gói quà</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">类型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奖励配置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">发放天数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">邮件ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tâm nguyện gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:590008:1#6:30002:1#3:100025:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cầu nguyện gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:590008:1#3:400036:10#3:20001:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:1:100#3:100022:2#0:0:1000000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -92,47 +91,88 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -206,7 +246,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -241,7 +280,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -417,90 +455,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="11.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="36" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" style="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+    <row r="2">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>130001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>130002</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2">
-        <v>130001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2">
-        <v>130002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="E4" t="n">
         <v>130003</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E4">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>